--- a/Financial Analysis/RCAT.xlsx
+++ b/Financial Analysis/RCAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D702D3-AFF0-4079-8218-29A64DC7F229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C990B7-162D-4361-85DA-256662DB20D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>RCAT</t>
   </si>
@@ -176,16 +176,26 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +228,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -264,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -283,6 +302,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,14 +751,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>10</v>
+        <v>11.52</v>
       </c>
       <c r="E3" s="6">
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="G3" s="6">
         <v>45975</v>
@@ -761,7 +782,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1178</v>
+        <v>1357.0559999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -803,7 +824,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1131.9000000000001</v>
+        <v>1310.9559999999999</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397894AD-87FB-4692-8DE7-D99492332738}">
-  <dimension ref="B2:ED28"/>
+  <dimension ref="B2:ED32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -947,7 +968,7 @@
         <v>869.43780000000004</v>
       </c>
       <c r="W3" s="9">
-        <f t="shared" ref="W3:Y3" si="0">V3*1.3</f>
+        <f t="shared" ref="W3" si="0">V3*1.3</f>
         <v>1130.2691400000001</v>
       </c>
       <c r="X3" s="9">
@@ -2463,7 +2484,7 @@
         <v>34</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" ref="F20:H20" si="21">F5/F3</f>
+        <f t="shared" ref="F20:G20" si="21">F5/F3</f>
         <v>-6.6666666666666721E-2</v>
       </c>
       <c r="G20" s="10">
@@ -2594,7 +2615,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" ref="F22:H22" si="25">F7/F3</f>
+        <f t="shared" ref="F22:G22" si="25">F7/F3</f>
         <v>1.5333333333333332</v>
       </c>
       <c r="G22" s="10">
@@ -2727,7 +2748,7 @@
         <v>38</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" ref="F24:H24" si="29">F11/F3</f>
+        <f t="shared" ref="F24:G24" si="29">F11/F3</f>
         <v>-6.333333333333333</v>
       </c>
       <c r="G24" s="10">
@@ -2815,7 +2836,7 @@
         <v>39</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" ref="F26:H26" si="32">F15/F3</f>
+        <f t="shared" ref="F26:G26" si="32">F15/F3</f>
         <v>-9.1333333333333329</v>
       </c>
       <c r="G26" s="10">
@@ -2883,7 +2904,7 @@
       </c>
       <c r="AB26" s="3">
         <f>Main!D3</f>
-        <v>10</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.3">
@@ -2892,7 +2913,7 @@
       </c>
       <c r="AB27" s="11">
         <f>AB25/AB26-1</f>
-        <v>-0.85432485058235097</v>
+        <v>-0.87354587724162402</v>
       </c>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.3">
@@ -2901,6 +2922,36 @@
       </c>
       <c r="AB28" s="7" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="12">
+        <f>55.6</f>
+        <v>55.6</v>
+      </c>
+      <c r="H29" s="12">
+        <v>121.4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" s="13">
+        <f>Main!D9/Model!H29</f>
+        <v>10.798649093904446</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="10">
+        <f>H29/Main!D9-1</f>
+        <v>-0.90739582411614117</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RCAT.xlsx
+++ b/Financial Analysis/RCAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C990B7-162D-4361-85DA-256662DB20D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92960BD6-BC87-438C-8BC8-4988E7C7B0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
   </bookViews>
@@ -758,7 +758,7 @@
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45933</v>
+        <v>45955</v>
       </c>
       <c r="G3" s="6">
         <v>45975</v>

--- a/Financial Analysis/RCAT.xlsx
+++ b/Financial Analysis/RCAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92960BD6-BC87-438C-8BC8-4988E7C7B0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9A9DCE-D65A-4535-8802-16EEF59C7B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -175,9 +175,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
-  </si>
-  <si>
     <t>L+S/E</t>
   </si>
   <si>
@@ -185,6 +182,9 @@
   </si>
   <si>
     <t>B/EV</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -325,13 +325,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -349,7 +349,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5516880" y="15240"/>
+          <a:off x="6126480" y="15240"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -375,13 +375,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -399,7 +399,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9791700" y="7620"/>
+          <a:off x="9182100" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -751,17 +751,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>11.52</v>
+        <v>6.36</v>
       </c>
       <c r="E3" s="6">
-        <v>45933</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45955</v>
+        <v>45983</v>
       </c>
       <c r="G3" s="6">
-        <v>45975</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -769,11 +769,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>99.8+18</f>
-        <v>117.8</v>
+        <f>119.4</f>
+        <v>119.4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -782,7 +782,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>1357.0559999999998</v>
+        <v>759.38400000000013</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -790,11 +790,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>65.9</f>
-        <v>65.900000000000006</v>
+        <f>206.4</f>
+        <v>206.4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -802,11 +802,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>0.4+19.4</f>
-        <v>19.799999999999997</v>
+        <f>0.4+13.4</f>
+        <v>13.8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -815,7 +815,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>46.100000000000009</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +824,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1310.9559999999999</v>
+        <v>566.78400000000011</v>
       </c>
     </row>
   </sheetData>
@@ -920,6 +920,9 @@
       <c r="D3" s="9">
         <v>6.4</v>
       </c>
+      <c r="E3" s="9">
+        <v>1.3</v>
+      </c>
       <c r="F3" s="9">
         <v>1.5</v>
       </c>
@@ -930,54 +933,59 @@
         <v>3.2</v>
       </c>
       <c r="I3" s="9">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="J3" s="9">
-        <v>4</v>
+        <f>F3*6.5</f>
+        <v>9.75</v>
+      </c>
+      <c r="N3" s="9">
+        <f>SUM(C3:F3)</f>
+        <v>15.8</v>
       </c>
       <c r="O3" s="9">
         <f>SUM(G3:J3)</f>
-        <v>12.3</v>
+        <v>24.15</v>
       </c>
       <c r="P3" s="9">
         <f>O3*2.5</f>
-        <v>30.75</v>
+        <v>60.375</v>
       </c>
       <c r="Q3" s="9">
-        <f>P3*2.2</f>
-        <v>67.650000000000006</v>
+        <f>P3*2</f>
+        <v>120.75</v>
       </c>
       <c r="R3" s="9">
-        <f>Q3*2</f>
-        <v>135.30000000000001</v>
+        <f>Q3*1.9</f>
+        <v>229.42499999999998</v>
       </c>
       <c r="S3" s="9">
         <f>R3*1.8</f>
-        <v>243.54000000000002</v>
+        <v>412.96499999999997</v>
       </c>
       <c r="T3" s="9">
         <f>S3*1.7</f>
-        <v>414.01800000000003</v>
+        <v>702.04049999999995</v>
       </c>
       <c r="U3" s="9">
         <f>T3*1.5</f>
-        <v>621.02700000000004</v>
+        <v>1053.0607499999999</v>
       </c>
       <c r="V3" s="9">
-        <f>U3*1.4</f>
-        <v>869.43780000000004</v>
+        <f>U3*1.35</f>
+        <v>1421.6320125</v>
       </c>
       <c r="W3" s="9">
-        <f t="shared" ref="W3" si="0">V3*1.3</f>
-        <v>1130.2691400000001</v>
+        <f>V3*1.25</f>
+        <v>1777.040015625</v>
       </c>
       <c r="X3" s="9">
-        <f>W3*1.2</f>
-        <v>1356.3229680000002</v>
+        <f>W3*1.18</f>
+        <v>2096.9072184375</v>
       </c>
       <c r="Y3" s="9">
-        <f>X3*1.15</f>
-        <v>1559.7714132000001</v>
+        <f>X3*1.12</f>
+        <v>2348.5360846500002</v>
       </c>
     </row>
     <row r="4" spans="2:134" x14ac:dyDescent="0.3">
@@ -990,6 +998,9 @@
       <c r="D4" s="4">
         <v>6.2</v>
       </c>
+      <c r="E4" s="4">
+        <v>1.7</v>
+      </c>
       <c r="F4" s="4">
         <v>1.6</v>
       </c>
@@ -1000,56 +1011,59 @@
         <v>2.8</v>
       </c>
       <c r="I4" s="4">
-        <f>I3*0.85</f>
-        <v>2.9750000000000001</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4">
-        <f t="shared" ref="J4" si="1">J3*0.85</f>
-        <v>3.4</v>
+        <f t="shared" ref="J4" si="0">J3*0.85</f>
+        <v>8.2874999999999996</v>
+      </c>
+      <c r="N4" s="4">
+        <f>SUM(C4:F4)</f>
+        <v>14.999999999999998</v>
       </c>
       <c r="O4" s="4">
         <f>SUM(G4:J4)</f>
-        <v>11.675000000000001</v>
+        <v>22.587499999999999</v>
       </c>
       <c r="P4" s="4">
         <f>P3-P5</f>
-        <v>24.907499999999999</v>
+        <v>51.318750000000001</v>
       </c>
       <c r="Q4" s="4">
-        <f t="shared" ref="Q4:Y4" si="2">Q3-Q5</f>
-        <v>51.414000000000001</v>
+        <f t="shared" ref="Q4:Y4" si="1">Q3-Q5</f>
+        <v>96.6</v>
       </c>
       <c r="R4" s="4">
-        <f t="shared" si="2"/>
-        <v>98.769000000000005</v>
+        <f t="shared" si="1"/>
+        <v>172.06874999999999</v>
       </c>
       <c r="S4" s="4">
-        <f t="shared" si="2"/>
-        <v>175.34880000000001</v>
+        <f t="shared" si="1"/>
+        <v>297.33479999999997</v>
       </c>
       <c r="T4" s="4">
-        <f t="shared" si="2"/>
-        <v>289.81260000000003</v>
+        <f t="shared" si="1"/>
+        <v>491.42834999999997</v>
       </c>
       <c r="U4" s="4">
-        <f t="shared" si="2"/>
-        <v>434.71890000000008</v>
+        <f t="shared" si="1"/>
+        <v>737.14252499999998</v>
       </c>
       <c r="V4" s="4">
-        <f t="shared" si="2"/>
-        <v>608.60645999999997</v>
+        <f t="shared" si="1"/>
+        <v>995.14240874999996</v>
       </c>
       <c r="W4" s="4">
-        <f t="shared" si="2"/>
-        <v>791.18839800000001</v>
+        <f t="shared" si="1"/>
+        <v>1243.9280109374999</v>
       </c>
       <c r="X4" s="4">
-        <f t="shared" si="2"/>
-        <v>949.4260776000001</v>
+        <f t="shared" si="1"/>
+        <v>1467.83505290625</v>
       </c>
       <c r="Y4" s="4">
-        <f t="shared" si="2"/>
-        <v>1091.83998924</v>
+        <f t="shared" si="1"/>
+        <v>1643.9752592550003</v>
       </c>
     </row>
     <row r="5" spans="2:134" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1064,6 +1078,10 @@
         <f>D3-D4</f>
         <v>0.20000000000000018</v>
       </c>
+      <c r="E5" s="9">
+        <f t="shared" ref="E5" si="2">E3-E4</f>
+        <v>-0.39999999999999991</v>
+      </c>
       <c r="F5" s="9">
         <f>F3-F4</f>
         <v>-0.10000000000000009</v>
@@ -1078,55 +1096,59 @@
       </c>
       <c r="I5" s="9">
         <f t="shared" ref="I5:J5" si="3">I3-I4</f>
-        <v>0.52499999999999991</v>
+        <v>0.59999999999999964</v>
       </c>
       <c r="J5" s="9">
         <f t="shared" si="3"/>
-        <v>0.60000000000000009</v>
+        <v>1.4625000000000004</v>
+      </c>
+      <c r="N5" s="9">
+        <f>N3-N4</f>
+        <v>0.80000000000000249</v>
       </c>
       <c r="O5" s="9">
         <f>O3-O4</f>
-        <v>0.625</v>
+        <v>1.5625</v>
       </c>
       <c r="P5" s="9">
-        <f>P3*0.19</f>
-        <v>5.8425000000000002</v>
+        <f>P3*0.15</f>
+        <v>9.0562500000000004</v>
       </c>
       <c r="Q5" s="9">
-        <f>Q3*0.24</f>
-        <v>16.236000000000001</v>
+        <f>Q3*0.2</f>
+        <v>24.150000000000002</v>
       </c>
       <c r="R5" s="9">
-        <f>R3*0.27</f>
-        <v>36.531000000000006</v>
+        <f>R3*0.25</f>
+        <v>57.356249999999996</v>
       </c>
       <c r="S5" s="9">
         <f>S3*0.28</f>
-        <v>68.191200000000009</v>
+        <v>115.6302</v>
       </c>
       <c r="T5" s="9">
         <f>T3*0.3</f>
-        <v>124.2054</v>
+        <v>210.61214999999999</v>
       </c>
       <c r="U5" s="9">
         <f t="shared" ref="U5:Y5" si="4">U3*0.3</f>
-        <v>186.3081</v>
+        <v>315.91822499999995</v>
       </c>
       <c r="V5" s="9">
         <f t="shared" si="4"/>
-        <v>260.83134000000001</v>
+        <v>426.48960374999996</v>
       </c>
       <c r="W5" s="9">
         <f t="shared" si="4"/>
-        <v>339.08074200000004</v>
+        <v>533.11200468749996</v>
       </c>
       <c r="X5" s="9">
         <f t="shared" si="4"/>
-        <v>406.89689040000002</v>
+        <v>629.07216553124999</v>
       </c>
       <c r="Y5" s="9">
         <f t="shared" si="4"/>
-        <v>467.93142396000002</v>
+        <v>704.56082539500005</v>
       </c>
     </row>
     <row r="6" spans="2:134" x14ac:dyDescent="0.3">
@@ -1139,6 +1161,9 @@
       <c r="D6" s="4">
         <v>0.3</v>
       </c>
+      <c r="E6" s="4">
+        <v>1.9</v>
+      </c>
       <c r="F6" s="4">
         <v>2.2000000000000002</v>
       </c>
@@ -1149,54 +1174,58 @@
         <v>3.6</v>
       </c>
       <c r="I6" s="4">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4">
         <v>4</v>
       </c>
+      <c r="N6" s="4">
+        <f t="shared" ref="N6:N9" si="5">SUM(C6:F6)</f>
+        <v>7.1000000000000005</v>
+      </c>
       <c r="O6" s="4">
-        <f t="shared" ref="O6:O9" si="5">SUM(G6:J6)</f>
-        <v>14.8</v>
+        <f t="shared" ref="O6:O9" si="6">SUM(G6:J6)</f>
+        <v>17</v>
       </c>
       <c r="P6" s="4">
         <f>O6*1.6</f>
-        <v>23.680000000000003</v>
+        <v>27.200000000000003</v>
       </c>
       <c r="Q6" s="4">
         <f>P6*1.4</f>
-        <v>33.152000000000001</v>
+        <v>38.08</v>
       </c>
       <c r="R6" s="4">
         <f>Q6*1.3</f>
-        <v>43.0976</v>
+        <v>49.503999999999998</v>
       </c>
       <c r="S6" s="4">
         <f>R6*1.2</f>
-        <v>51.717120000000001</v>
+        <v>59.404799999999994</v>
       </c>
       <c r="T6" s="4">
         <f>S6*1.1</f>
-        <v>56.888832000000008</v>
+        <v>65.345280000000002</v>
       </c>
       <c r="U6" s="4">
         <f>T6*1.05</f>
-        <v>59.733273600000011</v>
+        <v>68.612544</v>
       </c>
       <c r="V6" s="4">
-        <f t="shared" ref="V6:Y6" si="6">U6*1.05</f>
-        <v>62.719937280000018</v>
+        <f t="shared" ref="V6:Y6" si="7">U6*1.05</f>
+        <v>72.043171200000003</v>
       </c>
       <c r="W6" s="4">
-        <f t="shared" si="6"/>
-        <v>65.855934144000017</v>
+        <f t="shared" si="7"/>
+        <v>75.64532976000001</v>
       </c>
       <c r="X6" s="4">
-        <f t="shared" si="6"/>
-        <v>69.148730851200014</v>
+        <f t="shared" si="7"/>
+        <v>79.427596248000015</v>
       </c>
       <c r="Y6" s="4">
-        <f t="shared" si="6"/>
-        <v>72.606167393760018</v>
+        <f t="shared" si="7"/>
+        <v>83.398976060400017</v>
       </c>
     </row>
     <row r="7" spans="2:134" x14ac:dyDescent="0.3">
@@ -1209,6 +1238,9 @@
       <c r="D7" s="4">
         <v>2.2000000000000002</v>
       </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
       <c r="F7" s="4">
         <v>2.2999999999999998</v>
       </c>
@@ -1219,56 +1251,59 @@
         <v>3.2</v>
       </c>
       <c r="I7" s="4">
-        <f>I3*0.9</f>
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4">
-        <f>J3*0.85</f>
-        <v>3.4</v>
+        <f>J3*0.4</f>
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="N7" s="4">
+        <f t="shared" si="5"/>
+        <v>7.8999999999999995</v>
       </c>
       <c r="O7" s="4">
-        <f t="shared" si="5"/>
-        <v>13.05</v>
+        <f t="shared" si="6"/>
+        <v>13.4</v>
       </c>
       <c r="P7" s="4">
-        <f>P3*0.6</f>
-        <v>18.45</v>
+        <f>P3*0.5</f>
+        <v>30.1875</v>
       </c>
       <c r="Q7" s="4">
         <f>Q3*0.4</f>
-        <v>27.060000000000002</v>
+        <v>48.300000000000004</v>
       </c>
       <c r="R7" s="4">
         <f>R3*0.3</f>
-        <v>40.590000000000003</v>
+        <v>68.827499999999986</v>
       </c>
       <c r="S7" s="4">
         <f>S3*0.2</f>
-        <v>48.708000000000006</v>
+        <v>82.593000000000004</v>
       </c>
       <c r="T7" s="4">
         <f>T3*0.15</f>
-        <v>62.102699999999999</v>
+        <v>105.30607499999999</v>
       </c>
       <c r="U7" s="4">
         <f>U3*0.13</f>
-        <v>80.73351000000001</v>
+        <v>136.8978975</v>
       </c>
       <c r="V7" s="4">
         <f>V3*0.11</f>
-        <v>95.638158000000004</v>
+        <v>156.379521375</v>
       </c>
       <c r="W7" s="4">
         <f>W3*0.1</f>
-        <v>113.02691400000002</v>
+        <v>177.70400156250003</v>
       </c>
       <c r="X7" s="4">
         <f>X3*0.09</f>
-        <v>122.06906712000001</v>
+        <v>188.721649659375</v>
       </c>
       <c r="Y7" s="4">
         <f>Y3*0.09</f>
-        <v>140.37942718799999</v>
+        <v>211.36824761850002</v>
       </c>
     </row>
     <row r="8" spans="2:134" x14ac:dyDescent="0.3">
@@ -1281,6 +1316,9 @@
       <c r="D8" s="4">
         <v>2.7</v>
       </c>
+      <c r="E8" s="4">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="F8" s="4">
         <v>4.5</v>
       </c>
@@ -1291,54 +1329,58 @@
         <v>6.2</v>
       </c>
       <c r="I8" s="4">
-        <v>6.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J8" s="4">
         <v>7.3</v>
       </c>
+      <c r="N8" s="4">
+        <f t="shared" si="5"/>
+        <v>14.4</v>
+      </c>
       <c r="O8" s="4">
-        <f t="shared" si="5"/>
-        <v>24.900000000000002</v>
+        <f t="shared" si="6"/>
+        <v>27.6</v>
       </c>
       <c r="P8" s="4">
         <f>O8*1.5</f>
-        <v>37.35</v>
+        <v>41.400000000000006</v>
       </c>
       <c r="Q8" s="4">
         <f>P8*1.3</f>
-        <v>48.555000000000007</v>
+        <v>53.820000000000007</v>
       </c>
       <c r="R8" s="4">
         <f>Q8*1.2</f>
-        <v>58.266000000000005</v>
+        <v>64.584000000000003</v>
       </c>
       <c r="S8" s="4">
         <f>R8*1.15</f>
-        <v>67.005899999999997</v>
+        <v>74.271599999999992</v>
       </c>
       <c r="T8" s="4">
         <f>S8*1.1</f>
-        <v>73.706490000000002</v>
+        <v>81.698759999999993</v>
       </c>
       <c r="U8" s="4">
         <f>T8*1.05</f>
-        <v>77.39181450000001</v>
+        <v>85.783698000000001</v>
       </c>
       <c r="V8" s="4">
         <f>U8*1.04</f>
-        <v>80.487487080000008</v>
+        <v>89.215045920000009</v>
       </c>
       <c r="W8" s="4">
         <f>V8*1.03</f>
-        <v>82.902111692400013</v>
+        <v>91.891497297600012</v>
       </c>
       <c r="X8" s="4">
-        <f t="shared" ref="X8:Y8" si="7">W8*1.03</f>
-        <v>85.389175043172017</v>
+        <f t="shared" ref="X8:Y8" si="8">W8*1.03</f>
+        <v>94.648242216528018</v>
       </c>
       <c r="Y8" s="4">
-        <f t="shared" si="7"/>
-        <v>87.950850294467173</v>
+        <f t="shared" si="8"/>
+        <v>97.487689483023857</v>
       </c>
     </row>
     <row r="9" spans="2:134" x14ac:dyDescent="0.3">
@@ -1351,6 +1393,9 @@
       <c r="D9" s="4">
         <v>0.4</v>
       </c>
+      <c r="E9" s="4">
+        <v>0.1</v>
+      </c>
       <c r="F9" s="4">
         <v>0.4</v>
       </c>
@@ -1366,8 +1411,12 @@
       <c r="J9" s="4">
         <v>0</v>
       </c>
+      <c r="N9" s="4">
+        <f t="shared" si="5"/>
+        <v>0.9</v>
+      </c>
       <c r="O9" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P9" s="4">
@@ -1413,6 +1462,10 @@
         <f>SUM(D6:D9)</f>
         <v>5.6000000000000005</v>
       </c>
+      <c r="E10" s="4">
+        <f t="shared" ref="E10" si="9">SUM(E6:E9)</f>
+        <v>8.1</v>
+      </c>
       <c r="F10" s="4">
         <f>SUM(F6:F9)</f>
         <v>9.4</v>
@@ -1426,56 +1479,60 @@
         <v>13</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" ref="I10:J10" si="8">SUM(I6:I9)</f>
-        <v>13.45</v>
+        <f t="shared" ref="I10:J10" si="10">SUM(I6:I9)</f>
+        <v>18.2</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="8"/>
-        <v>14.7</v>
+        <f t="shared" si="10"/>
+        <v>15.2</v>
+      </c>
+      <c r="N10" s="4">
+        <f>SUM(N6:N9)</f>
+        <v>30.299999999999997</v>
       </c>
       <c r="O10" s="4">
         <f>SUM(O6:O9)</f>
-        <v>52.75</v>
+        <v>58</v>
       </c>
       <c r="P10" s="4">
         <f>SUM(P6:P9)</f>
-        <v>79.48</v>
+        <v>98.787500000000009</v>
       </c>
       <c r="Q10" s="4">
-        <f t="shared" ref="Q10:Y10" si="9">SUM(Q6:Q9)</f>
-        <v>108.76700000000001</v>
+        <f t="shared" ref="Q10:Y10" si="11">SUM(Q6:Q9)</f>
+        <v>140.19999999999999</v>
       </c>
       <c r="R10" s="4">
-        <f t="shared" si="9"/>
-        <v>141.95359999999999</v>
+        <f t="shared" si="11"/>
+        <v>182.91549999999998</v>
       </c>
       <c r="S10" s="4">
-        <f t="shared" si="9"/>
-        <v>167.43101999999999</v>
+        <f t="shared" si="11"/>
+        <v>216.26939999999996</v>
       </c>
       <c r="T10" s="4">
-        <f t="shared" si="9"/>
-        <v>192.69802200000001</v>
+        <f t="shared" si="11"/>
+        <v>252.35011499999999</v>
       </c>
       <c r="U10" s="4">
-        <f t="shared" si="9"/>
-        <v>217.85859810000002</v>
+        <f t="shared" si="11"/>
+        <v>291.29413950000003</v>
       </c>
       <c r="V10" s="4">
-        <f t="shared" si="9"/>
-        <v>238.84558236000004</v>
+        <f t="shared" si="11"/>
+        <v>317.63773849500001</v>
       </c>
       <c r="W10" s="4">
-        <f t="shared" si="9"/>
-        <v>261.78495983640005</v>
+        <f t="shared" si="11"/>
+        <v>345.24082862010005</v>
       </c>
       <c r="X10" s="4">
-        <f t="shared" si="9"/>
-        <v>276.60697301437204</v>
+        <f t="shared" si="11"/>
+        <v>362.79748812390301</v>
       </c>
       <c r="Y10" s="4">
-        <f t="shared" si="9"/>
-        <v>300.9364448762272</v>
+        <f t="shared" si="11"/>
+        <v>392.25491316192392</v>
       </c>
     </row>
     <row r="11" spans="2:134" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1490,6 +1547,10 @@
         <f>D5-D10</f>
         <v>-5.4</v>
       </c>
+      <c r="E11" s="9">
+        <f t="shared" ref="E11" si="12">E5-E10</f>
+        <v>-8.5</v>
+      </c>
       <c r="F11" s="9">
         <f>F5-F10</f>
         <v>-9.5</v>
@@ -1503,56 +1564,60 @@
         <v>-12.6</v>
       </c>
       <c r="I11" s="9">
-        <f t="shared" ref="I11:J11" si="10">I5-I10</f>
-        <v>-12.924999999999999</v>
+        <f t="shared" ref="I11:J11" si="13">I5-I10</f>
+        <v>-17.600000000000001</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" si="10"/>
-        <v>-14.1</v>
+        <f t="shared" si="13"/>
+        <v>-13.737499999999999</v>
+      </c>
+      <c r="N11" s="9">
+        <f>N5-N10</f>
+        <v>-29.499999999999993</v>
       </c>
       <c r="O11" s="9">
         <f>O5-O10</f>
-        <v>-52.125</v>
+        <v>-56.4375</v>
       </c>
       <c r="P11" s="9">
         <f>P5-P10</f>
-        <v>-73.637500000000003</v>
+        <v>-89.731250000000003</v>
       </c>
       <c r="Q11" s="9">
-        <f t="shared" ref="Q11:Y11" si="11">Q5-Q10</f>
-        <v>-92.531000000000006</v>
+        <f t="shared" ref="Q11:Y11" si="14">Q5-Q10</f>
+        <v>-116.04999999999998</v>
       </c>
       <c r="R11" s="9">
-        <f t="shared" si="11"/>
-        <v>-105.42259999999999</v>
+        <f t="shared" si="14"/>
+        <v>-125.55924999999999</v>
       </c>
       <c r="S11" s="9">
-        <f t="shared" si="11"/>
-        <v>-99.23981999999998</v>
+        <f t="shared" si="14"/>
+        <v>-100.63919999999996</v>
       </c>
       <c r="T11" s="9">
-        <f t="shared" si="11"/>
-        <v>-68.492622000000011</v>
+        <f t="shared" si="14"/>
+        <v>-41.737965000000003</v>
       </c>
       <c r="U11" s="9">
-        <f t="shared" si="11"/>
-        <v>-31.550498100000027</v>
+        <f t="shared" si="14"/>
+        <v>24.624085499999921</v>
       </c>
       <c r="V11" s="9">
-        <f t="shared" si="11"/>
-        <v>21.985757639999974</v>
+        <f t="shared" si="14"/>
+        <v>108.85186525499995</v>
       </c>
       <c r="W11" s="9">
-        <f t="shared" si="11"/>
-        <v>77.295782163599995</v>
+        <f t="shared" si="14"/>
+        <v>187.87117606739992</v>
       </c>
       <c r="X11" s="9">
-        <f t="shared" si="11"/>
-        <v>130.28991738562797</v>
+        <f t="shared" si="14"/>
+        <v>266.27467740734699</v>
       </c>
       <c r="Y11" s="9">
-        <f t="shared" si="11"/>
-        <v>166.99497908377282</v>
+        <f t="shared" si="14"/>
+        <v>312.30591223307613</v>
       </c>
     </row>
     <row r="12" spans="2:134" x14ac:dyDescent="0.3">
@@ -1565,6 +1630,9 @@
       <c r="D12" s="4">
         <v>2.8</v>
       </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
       <c r="F12" s="4">
         <v>4.2</v>
       </c>
@@ -1575,54 +1643,58 @@
         <v>0.6</v>
       </c>
       <c r="I12" s="4">
-        <v>2</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="J12" s="4">
         <v>4</v>
       </c>
+      <c r="N12" s="4">
+        <f>SUM(C12:F12)</f>
+        <v>10.399999999999999</v>
+      </c>
       <c r="O12" s="4">
         <f>SUM(G12:J12)</f>
-        <v>17.2</v>
+        <v>13</v>
       </c>
       <c r="P12" s="4">
         <f>O12*1.02</f>
-        <v>17.544</v>
+        <v>13.26</v>
       </c>
       <c r="Q12" s="4">
-        <f t="shared" ref="Q12:Y12" si="12">P12*1.02</f>
-        <v>17.894880000000001</v>
+        <f t="shared" ref="Q12:Y12" si="15">P12*1.02</f>
+        <v>13.5252</v>
       </c>
       <c r="R12" s="4">
-        <f t="shared" si="12"/>
-        <v>18.252777600000002</v>
+        <f t="shared" si="15"/>
+        <v>13.795704000000001</v>
       </c>
       <c r="S12" s="4">
-        <f t="shared" si="12"/>
-        <v>18.617833152000003</v>
+        <f t="shared" si="15"/>
+        <v>14.07161808</v>
       </c>
       <c r="T12" s="4">
-        <f t="shared" si="12"/>
-        <v>18.990189815040004</v>
+        <f t="shared" si="15"/>
+        <v>14.353050441600001</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" si="12"/>
-        <v>19.369993611340806</v>
+        <f t="shared" si="15"/>
+        <v>14.640111450432</v>
       </c>
       <c r="V12" s="4">
-        <f t="shared" si="12"/>
-        <v>19.757393483567622</v>
+        <f t="shared" si="15"/>
+        <v>14.93291367944064</v>
       </c>
       <c r="W12" s="4">
-        <f t="shared" si="12"/>
-        <v>20.152541353238973</v>
+        <f t="shared" si="15"/>
+        <v>15.231571953029453</v>
       </c>
       <c r="X12" s="4">
-        <f t="shared" si="12"/>
-        <v>20.555592180303755</v>
+        <f t="shared" si="15"/>
+        <v>15.536203392090043</v>
       </c>
       <c r="Y12" s="4">
-        <f t="shared" si="12"/>
-        <v>20.966704023909831</v>
+        <f t="shared" si="15"/>
+        <v>15.846927459931845</v>
       </c>
     </row>
     <row r="13" spans="2:134" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1637,6 +1709,10 @@
         <f>D11-D12</f>
         <v>-8.1999999999999993</v>
       </c>
+      <c r="E13" s="9">
+        <f t="shared" ref="E13" si="16">E11-E12</f>
+        <v>-12.5</v>
+      </c>
       <c r="F13" s="9">
         <f>F11-F12</f>
         <v>-13.7</v>
@@ -1650,56 +1726,60 @@
         <v>-13.2</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" ref="I13:J13" si="13">I11-I12</f>
-        <v>-14.924999999999999</v>
+        <f t="shared" ref="I13:J13" si="17">I11-I12</f>
+        <v>-15.400000000000002</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="13"/>
-        <v>-18.100000000000001</v>
+        <f t="shared" si="17"/>
+        <v>-17.737499999999997</v>
+      </c>
+      <c r="N13" s="9">
+        <f>N11-N12</f>
+        <v>-39.899999999999991</v>
       </c>
       <c r="O13" s="9">
         <f>O11-O12</f>
-        <v>-69.325000000000003</v>
+        <v>-69.4375</v>
       </c>
       <c r="P13" s="9">
         <f>P11-P12</f>
-        <v>-91.1815</v>
+        <v>-102.99125000000001</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" ref="Q13:Y13" si="14">Q11-Q12</f>
-        <v>-110.42588000000001</v>
+        <f t="shared" ref="Q13:Y13" si="18">Q11-Q12</f>
+        <v>-129.5752</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="14"/>
-        <v>-123.67537759999999</v>
+        <f t="shared" si="18"/>
+        <v>-139.35495399999999</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="14"/>
-        <v>-117.85765315199998</v>
+        <f t="shared" si="18"/>
+        <v>-114.71081807999997</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="14"/>
-        <v>-87.482811815040009</v>
+        <f t="shared" si="18"/>
+        <v>-56.091015441600007</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="14"/>
-        <v>-50.92049171134083</v>
+        <f t="shared" si="18"/>
+        <v>9.9839740495679212</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" si="14"/>
-        <v>2.2283641564323524</v>
+        <f t="shared" si="18"/>
+        <v>93.918951575559305</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="14"/>
-        <v>57.143240810361021</v>
+        <f t="shared" si="18"/>
+        <v>172.63960411437046</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" si="14"/>
-        <v>109.73432520532421</v>
+        <f t="shared" si="18"/>
+        <v>250.73847401525694</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" si="14"/>
-        <v>146.02827505986298</v>
+        <f t="shared" si="18"/>
+        <v>296.45898477314427</v>
       </c>
     </row>
     <row r="14" spans="2:134" x14ac:dyDescent="0.3">
@@ -1712,6 +1792,9 @@
       <c r="D14" s="4">
         <v>0</v>
       </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
       <c r="F14" s="4">
         <v>0</v>
       </c>
@@ -1722,14 +1805,18 @@
         <v>0</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <f>SUM(C14:F14)</f>
         <v>0</v>
       </c>
       <c r="O14" s="4">
         <f>SUM(G14:J14)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P14" s="4">
         <v>0</v>
@@ -1767,512 +1854,520 @@
         <v>24</v>
       </c>
       <c r="C15" s="9">
-        <f>C13-C14</f>
+        <f t="shared" ref="C15:J15" si="19">C13-C14</f>
         <v>-5.5</v>
       </c>
       <c r="D15" s="9">
-        <f>D13-D14</f>
+        <f t="shared" si="19"/>
         <v>-8.1999999999999993</v>
       </c>
+      <c r="E15" s="9">
+        <f t="shared" si="19"/>
+        <v>-12.5</v>
+      </c>
       <c r="F15" s="9">
-        <f>F13-F14</f>
+        <f t="shared" si="19"/>
         <v>-13.7</v>
       </c>
       <c r="G15" s="9">
-        <f>G13-G14</f>
+        <f t="shared" si="19"/>
         <v>-23.1</v>
       </c>
       <c r="H15" s="9">
-        <f>H13-H14</f>
+        <f t="shared" si="19"/>
         <v>-13.2</v>
       </c>
       <c r="I15" s="9">
-        <f>I13-I14</f>
-        <v>-14.924999999999999</v>
+        <f t="shared" si="19"/>
+        <v>-16.100000000000001</v>
       </c>
       <c r="J15" s="9">
-        <f>J13-J14</f>
-        <v>-18.100000000000001</v>
+        <f t="shared" si="19"/>
+        <v>-17.737499999999997</v>
+      </c>
+      <c r="N15" s="9">
+        <f>N13-N14</f>
+        <v>-39.899999999999991</v>
       </c>
       <c r="O15" s="9">
         <f>O13-O14</f>
-        <v>-69.325000000000003</v>
+        <v>-70.137500000000003</v>
       </c>
       <c r="P15" s="9">
         <f>P13-P14</f>
-        <v>-91.1815</v>
+        <v>-102.99125000000001</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:Y15" si="15">Q13-Q14</f>
-        <v>-110.42588000000001</v>
+        <f t="shared" ref="Q15:Y15" si="20">Q13-Q14</f>
+        <v>-129.5752</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="15"/>
-        <v>-123.67537759999999</v>
+        <f t="shared" si="20"/>
+        <v>-139.35495399999999</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="15"/>
-        <v>-117.85765315199998</v>
+        <f t="shared" si="20"/>
+        <v>-114.71081807999997</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" si="15"/>
-        <v>-87.482811815040009</v>
+        <f t="shared" si="20"/>
+        <v>-56.091015441600007</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="15"/>
-        <v>-50.92049171134083</v>
+        <f t="shared" si="20"/>
+        <v>9.9839740495679212</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="15"/>
-        <v>2.2283641564323524</v>
+        <f t="shared" si="20"/>
+        <v>93.918951575559305</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="15"/>
-        <v>57.143240810361021</v>
+        <f t="shared" si="20"/>
+        <v>172.63960411437046</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="15"/>
-        <v>109.73432520532421</v>
+        <f t="shared" si="20"/>
+        <v>250.73847401525694</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="15"/>
-        <v>146.02827505986298</v>
+        <f t="shared" si="20"/>
+        <v>296.45898477314427</v>
       </c>
       <c r="Z15" s="2">
         <f>Y15*(1+$AB$20)</f>
-        <v>144.56799230926435</v>
+        <v>293.49439492541285</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" ref="AA15:CL15" si="16">Z15*(1+$AB$20)</f>
-        <v>143.1223123861717</v>
+        <f t="shared" ref="AA15:CL15" si="21">Z15*(1+$AB$20)</f>
+        <v>290.5594509761587</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="16"/>
-        <v>141.69108926230999</v>
+        <f t="shared" si="21"/>
+        <v>287.65385646639709</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="16"/>
-        <v>140.27417836968689</v>
+        <f t="shared" si="21"/>
+        <v>284.77731790173311</v>
       </c>
       <c r="AD15" s="2">
-        <f t="shared" si="16"/>
-        <v>138.87143658599001</v>
+        <f t="shared" si="21"/>
+        <v>281.92954472271578</v>
       </c>
       <c r="AE15" s="2">
-        <f t="shared" si="16"/>
-        <v>137.48272222013011</v>
+        <f t="shared" si="21"/>
+        <v>279.11024927548863</v>
       </c>
       <c r="AF15" s="2">
-        <f t="shared" si="16"/>
-        <v>136.10789499792881</v>
+        <f t="shared" si="21"/>
+        <v>276.31914678273375</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" si="16"/>
-        <v>134.74681604794952</v>
+        <f t="shared" si="21"/>
+        <v>273.55595531490644</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" si="16"/>
-        <v>133.39934788747001</v>
+        <f t="shared" si="21"/>
+        <v>270.82039576175737</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="16"/>
-        <v>132.06535440859531</v>
+        <f t="shared" si="21"/>
+        <v>268.1121918041398</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="16"/>
-        <v>130.74470086450935</v>
+        <f t="shared" si="21"/>
+        <v>265.43106988609838</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" si="16"/>
-        <v>129.43725385586427</v>
+        <f t="shared" si="21"/>
+        <v>262.77675918723742</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" si="16"/>
-        <v>128.14288131730564</v>
+        <f t="shared" si="21"/>
+        <v>260.14899159536503</v>
       </c>
       <c r="AM15" s="2">
-        <f t="shared" si="16"/>
-        <v>126.86145250413259</v>
+        <f t="shared" si="21"/>
+        <v>257.54750167941137</v>
       </c>
       <c r="AN15" s="2">
-        <f t="shared" si="16"/>
-        <v>125.59283797909126</v>
+        <f t="shared" si="21"/>
+        <v>254.97202666261725</v>
       </c>
       <c r="AO15" s="2">
-        <f t="shared" si="16"/>
-        <v>124.33690959930034</v>
+        <f t="shared" si="21"/>
+        <v>252.42230639599109</v>
       </c>
       <c r="AP15" s="2">
-        <f t="shared" si="16"/>
-        <v>123.09354050330734</v>
+        <f t="shared" si="21"/>
+        <v>249.89808333203118</v>
       </c>
       <c r="AQ15" s="2">
-        <f t="shared" si="16"/>
-        <v>121.86260509827426</v>
+        <f t="shared" si="21"/>
+        <v>247.39910249871087</v>
       </c>
       <c r="AR15" s="2">
-        <f t="shared" si="16"/>
-        <v>120.64397904729151</v>
+        <f t="shared" si="21"/>
+        <v>244.92511147372377</v>
       </c>
       <c r="AS15" s="2">
-        <f t="shared" si="16"/>
-        <v>119.4375392568186</v>
+        <f t="shared" si="21"/>
+        <v>242.47586035898652</v>
       </c>
       <c r="AT15" s="2">
-        <f t="shared" si="16"/>
-        <v>118.24316386425041</v>
+        <f t="shared" si="21"/>
+        <v>240.05110175539664</v>
       </c>
       <c r="AU15" s="2">
-        <f t="shared" si="16"/>
-        <v>117.06073222560791</v>
+        <f t="shared" si="21"/>
+        <v>237.65059073784266</v>
       </c>
       <c r="AV15" s="2">
-        <f t="shared" si="16"/>
-        <v>115.89012490335183</v>
+        <f t="shared" si="21"/>
+        <v>235.27408483046423</v>
       </c>
       <c r="AW15" s="2">
-        <f t="shared" si="16"/>
-        <v>114.73122365431831</v>
+        <f t="shared" si="21"/>
+        <v>232.92134398215958</v>
       </c>
       <c r="AX15" s="2">
-        <f t="shared" si="16"/>
-        <v>113.58391141777513</v>
+        <f t="shared" si="21"/>
+        <v>230.592130542338</v>
       </c>
       <c r="AY15" s="2">
-        <f t="shared" si="16"/>
-        <v>112.44807230359737</v>
+        <f t="shared" si="21"/>
+        <v>228.28620923691463</v>
       </c>
       <c r="AZ15" s="2">
-        <f t="shared" si="16"/>
-        <v>111.3235915805614</v>
+        <f t="shared" si="21"/>
+        <v>226.00334714454547</v>
       </c>
       <c r="BA15" s="2">
-        <f t="shared" si="16"/>
-        <v>110.21035566475578</v>
+        <f t="shared" si="21"/>
+        <v>223.7433136731</v>
       </c>
       <c r="BB15" s="2">
-        <f t="shared" si="16"/>
-        <v>109.10825210810822</v>
+        <f t="shared" si="21"/>
+        <v>221.50588053636901</v>
       </c>
       <c r="BC15" s="2">
-        <f t="shared" si="16"/>
-        <v>108.01716958702714</v>
+        <f t="shared" si="21"/>
+        <v>219.29082173100531</v>
       </c>
       <c r="BD15" s="2">
-        <f t="shared" si="16"/>
-        <v>106.93699789115686</v>
+        <f t="shared" si="21"/>
+        <v>217.09791351369526</v>
       </c>
       <c r="BE15" s="2">
-        <f t="shared" si="16"/>
-        <v>105.8676279122453</v>
+        <f t="shared" si="21"/>
+        <v>214.92693437855831</v>
       </c>
       <c r="BF15" s="2">
-        <f t="shared" si="16"/>
-        <v>104.80895163312285</v>
+        <f t="shared" si="21"/>
+        <v>212.77766503477272</v>
       </c>
       <c r="BG15" s="2">
-        <f t="shared" si="16"/>
-        <v>103.76086211679161</v>
+        <f t="shared" si="21"/>
+        <v>210.649888384425</v>
       </c>
       <c r="BH15" s="2">
-        <f t="shared" si="16"/>
-        <v>102.72325349562369</v>
+        <f t="shared" si="21"/>
+        <v>208.54338950058076</v>
       </c>
       <c r="BI15" s="2">
-        <f t="shared" si="16"/>
-        <v>101.69602096066745</v>
+        <f t="shared" si="21"/>
+        <v>206.45795560557494</v>
       </c>
       <c r="BJ15" s="2">
-        <f t="shared" si="16"/>
-        <v>100.67906075106077</v>
+        <f t="shared" si="21"/>
+        <v>204.39337604951919</v>
       </c>
       <c r="BK15" s="2">
-        <f t="shared" si="16"/>
-        <v>99.672270143550165</v>
+        <f t="shared" si="21"/>
+        <v>202.34944228902398</v>
       </c>
       <c r="BL15" s="2">
-        <f t="shared" si="16"/>
-        <v>98.675547442114663</v>
+        <f t="shared" si="21"/>
+        <v>200.32594786613373</v>
       </c>
       <c r="BM15" s="2">
-        <f t="shared" si="16"/>
-        <v>97.688791967693518</v>
+        <f t="shared" si="21"/>
+        <v>198.3226883874724</v>
       </c>
       <c r="BN15" s="2">
-        <f t="shared" si="16"/>
-        <v>96.711904048016578</v>
+        <f t="shared" si="21"/>
+        <v>196.33946150359768</v>
       </c>
       <c r="BO15" s="2">
-        <f t="shared" si="16"/>
-        <v>95.744785007536407</v>
+        <f t="shared" si="21"/>
+        <v>194.3760668885617</v>
       </c>
       <c r="BP15" s="2">
-        <f t="shared" si="16"/>
-        <v>94.787337157461039</v>
+        <f t="shared" si="21"/>
+        <v>192.43230621967606</v>
       </c>
       <c r="BQ15" s="2">
-        <f t="shared" si="16"/>
-        <v>93.839463785886423</v>
+        <f t="shared" si="21"/>
+        <v>190.50798315747932</v>
       </c>
       <c r="BR15" s="2">
-        <f t="shared" si="16"/>
-        <v>92.90106914802756</v>
+        <f t="shared" si="21"/>
+        <v>188.60290332590452</v>
       </c>
       <c r="BS15" s="2">
-        <f t="shared" si="16"/>
-        <v>91.972058456547288</v>
+        <f t="shared" si="21"/>
+        <v>186.71687429264549</v>
       </c>
       <c r="BT15" s="2">
-        <f t="shared" si="16"/>
-        <v>91.05233787198182</v>
+        <f t="shared" si="21"/>
+        <v>184.84970554971903</v>
       </c>
       <c r="BU15" s="2">
-        <f t="shared" si="16"/>
-        <v>90.141814493262004</v>
+        <f t="shared" si="21"/>
+        <v>183.00120849422183</v>
       </c>
       <c r="BV15" s="2">
-        <f t="shared" si="16"/>
-        <v>89.240396348329384</v>
+        <f t="shared" si="21"/>
+        <v>181.17119640927962</v>
       </c>
       <c r="BW15" s="2">
-        <f t="shared" si="16"/>
-        <v>88.347992384846094</v>
+        <f t="shared" si="21"/>
+        <v>179.35948444518681</v>
       </c>
       <c r="BX15" s="2">
-        <f t="shared" si="16"/>
-        <v>87.464512460997639</v>
+        <f t="shared" si="21"/>
+        <v>177.56588960073495</v>
       </c>
       <c r="BY15" s="2">
-        <f t="shared" si="16"/>
-        <v>86.589867336387655</v>
+        <f t="shared" si="21"/>
+        <v>175.79023070472761</v>
       </c>
       <c r="BZ15" s="2">
-        <f t="shared" si="16"/>
-        <v>85.723968663023783</v>
+        <f t="shared" si="21"/>
+        <v>174.03232839768032</v>
       </c>
       <c r="CA15" s="2">
-        <f t="shared" si="16"/>
-        <v>84.866728976393546</v>
+        <f t="shared" si="21"/>
+        <v>172.29200511370351</v>
       </c>
       <c r="CB15" s="2">
-        <f t="shared" si="16"/>
-        <v>84.018061686629608</v>
+        <f t="shared" si="21"/>
+        <v>170.56908506256647</v>
       </c>
       <c r="CC15" s="2">
-        <f t="shared" si="16"/>
-        <v>83.177881069763316</v>
+        <f t="shared" si="21"/>
+        <v>168.8633942119408</v>
       </c>
       <c r="CD15" s="2">
-        <f t="shared" si="16"/>
-        <v>82.346102259065688</v>
+        <f t="shared" si="21"/>
+        <v>167.17476026982138</v>
       </c>
       <c r="CE15" s="2">
-        <f t="shared" si="16"/>
-        <v>81.522641236475025</v>
+        <f t="shared" si="21"/>
+        <v>165.50301266712316</v>
       </c>
       <c r="CF15" s="2">
-        <f t="shared" si="16"/>
-        <v>80.707414824110273</v>
+        <f t="shared" si="21"/>
+        <v>163.84798254045194</v>
       </c>
       <c r="CG15" s="2">
-        <f t="shared" si="16"/>
-        <v>79.900340675869174</v>
+        <f t="shared" si="21"/>
+        <v>162.20950271504742</v>
       </c>
       <c r="CH15" s="2">
-        <f t="shared" si="16"/>
-        <v>79.101337269110488</v>
+        <f t="shared" si="21"/>
+        <v>160.58740768789696</v>
       </c>
       <c r="CI15" s="2">
-        <f t="shared" si="16"/>
-        <v>78.310323896419376</v>
+        <f t="shared" si="21"/>
+        <v>158.98153361101799</v>
       </c>
       <c r="CJ15" s="2">
-        <f t="shared" si="16"/>
-        <v>77.527220657455189</v>
+        <f t="shared" si="21"/>
+        <v>157.39171827490782</v>
       </c>
       <c r="CK15" s="2">
-        <f t="shared" si="16"/>
-        <v>76.751948450880633</v>
+        <f t="shared" si="21"/>
+        <v>155.81780109215873</v>
       </c>
       <c r="CL15" s="2">
-        <f t="shared" si="16"/>
-        <v>75.984428966371823</v>
+        <f t="shared" si="21"/>
+        <v>154.25962308123715</v>
       </c>
       <c r="CM15" s="2">
-        <f t="shared" ref="CM15:ED15" si="17">CL15*(1+$AB$20)</f>
-        <v>75.224584676708105</v>
+        <f t="shared" ref="CM15:ED15" si="22">CL15*(1+$AB$20)</f>
+        <v>152.71702685042479</v>
       </c>
       <c r="CN15" s="2">
-        <f t="shared" si="17"/>
-        <v>74.472338829941023</v>
+        <f t="shared" si="22"/>
+        <v>151.18985658192054</v>
       </c>
       <c r="CO15" s="2">
-        <f t="shared" si="17"/>
-        <v>73.727615441641618</v>
+        <f t="shared" si="22"/>
+        <v>149.67795801610134</v>
       </c>
       <c r="CP15" s="2">
-        <f t="shared" si="17"/>
-        <v>72.990339287225197</v>
+        <f t="shared" si="22"/>
+        <v>148.18117843594032</v>
       </c>
       <c r="CQ15" s="2">
-        <f t="shared" si="17"/>
-        <v>72.260435894352938</v>
+        <f t="shared" si="22"/>
+        <v>146.69936665158093</v>
       </c>
       <c r="CR15" s="2">
-        <f t="shared" si="17"/>
-        <v>71.53783153540941</v>
+        <f t="shared" si="22"/>
+        <v>145.23237298506513</v>
       </c>
       <c r="CS15" s="2">
-        <f t="shared" si="17"/>
-        <v>70.822453220055309</v>
+        <f t="shared" si="22"/>
+        <v>143.78004925521446</v>
       </c>
       <c r="CT15" s="2">
-        <f t="shared" si="17"/>
-        <v>70.114228687854748</v>
+        <f t="shared" si="22"/>
+        <v>142.34224876266231</v>
       </c>
       <c r="CU15" s="2">
-        <f t="shared" si="17"/>
-        <v>69.413086400976198</v>
+        <f t="shared" si="22"/>
+        <v>140.91882627503568</v>
       </c>
       <c r="CV15" s="2">
-        <f t="shared" si="17"/>
-        <v>68.718955536966433</v>
+        <f t="shared" si="22"/>
+        <v>139.50963801228534</v>
       </c>
       <c r="CW15" s="2">
-        <f t="shared" si="17"/>
-        <v>68.031765981596763</v>
+        <f t="shared" si="22"/>
+        <v>138.11454163216249</v>
       </c>
       <c r="CX15" s="2">
-        <f t="shared" si="17"/>
-        <v>67.351448321780794</v>
+        <f t="shared" si="22"/>
+        <v>136.73339621584086</v>
       </c>
       <c r="CY15" s="2">
-        <f t="shared" si="17"/>
-        <v>66.677933838562979</v>
+        <f t="shared" si="22"/>
+        <v>135.36606225368246</v>
       </c>
       <c r="CZ15" s="2">
-        <f t="shared" si="17"/>
-        <v>66.011154500177355</v>
+        <f t="shared" si="22"/>
+        <v>134.01240163114562</v>
       </c>
       <c r="DA15" s="2">
-        <f t="shared" si="17"/>
-        <v>65.351042955175586</v>
+        <f t="shared" si="22"/>
+        <v>132.67227761483417</v>
       </c>
       <c r="DB15" s="2">
-        <f t="shared" si="17"/>
-        <v>64.697532525623828</v>
+        <f t="shared" si="22"/>
+        <v>131.34555483868584</v>
       </c>
       <c r="DC15" s="2">
-        <f t="shared" si="17"/>
-        <v>64.050557200367592</v>
+        <f t="shared" si="22"/>
+        <v>130.03209929029899</v>
       </c>
       <c r="DD15" s="2">
-        <f t="shared" si="17"/>
-        <v>63.410051628363917</v>
+        <f t="shared" si="22"/>
+        <v>128.731778297396</v>
       </c>
       <c r="DE15" s="2">
-        <f t="shared" si="17"/>
-        <v>62.775951112080278</v>
+        <f t="shared" si="22"/>
+        <v>127.44446051442205</v>
       </c>
       <c r="DF15" s="2">
-        <f t="shared" si="17"/>
-        <v>62.148191600959478</v>
+        <f t="shared" si="22"/>
+        <v>126.17001590927782</v>
       </c>
       <c r="DG15" s="2">
-        <f t="shared" si="17"/>
-        <v>61.526709684949886</v>
+        <f t="shared" si="22"/>
+        <v>124.90831575018504</v>
       </c>
       <c r="DH15" s="2">
-        <f t="shared" si="17"/>
-        <v>60.911442588100385</v>
+        <f t="shared" si="22"/>
+        <v>123.65923259268318</v>
       </c>
       <c r="DI15" s="2">
-        <f t="shared" si="17"/>
-        <v>60.302328162219382</v>
+        <f t="shared" si="22"/>
+        <v>122.42264026675635</v>
       </c>
       <c r="DJ15" s="2">
-        <f t="shared" si="17"/>
-        <v>59.69930488059719</v>
+        <f t="shared" si="22"/>
+        <v>121.19841386408878</v>
       </c>
       <c r="DK15" s="2">
-        <f t="shared" si="17"/>
-        <v>59.102311831791219</v>
+        <f t="shared" si="22"/>
+        <v>119.98642972544789</v>
       </c>
       <c r="DL15" s="2">
-        <f t="shared" si="17"/>
-        <v>58.511288713473306</v>
+        <f t="shared" si="22"/>
+        <v>118.78656542819341</v>
       </c>
       <c r="DM15" s="2">
-        <f t="shared" si="17"/>
-        <v>57.926175826338572</v>
+        <f t="shared" si="22"/>
+        <v>117.59869977391148</v>
       </c>
       <c r="DN15" s="2">
-        <f t="shared" si="17"/>
-        <v>57.346914068075186</v>
+        <f t="shared" si="22"/>
+        <v>116.42271277617236</v>
       </c>
       <c r="DO15" s="2">
-        <f t="shared" si="17"/>
-        <v>56.773444927394436</v>
+        <f t="shared" si="22"/>
+        <v>115.25848564841064</v>
       </c>
       <c r="DP15" s="2">
-        <f t="shared" si="17"/>
-        <v>56.205710478120494</v>
+        <f t="shared" si="22"/>
+        <v>114.10590079192653</v>
       </c>
       <c r="DQ15" s="2">
-        <f t="shared" si="17"/>
-        <v>55.643653373339291</v>
+        <f t="shared" si="22"/>
+        <v>112.96484178400726</v>
       </c>
       <c r="DR15" s="2">
-        <f t="shared" si="17"/>
-        <v>55.087216839605894</v>
+        <f t="shared" si="22"/>
+        <v>111.83519336616719</v>
       </c>
       <c r="DS15" s="2">
-        <f t="shared" si="17"/>
-        <v>54.536344671209832</v>
+        <f t="shared" si="22"/>
+        <v>110.71684143250552</v>
       </c>
       <c r="DT15" s="2">
-        <f t="shared" si="17"/>
-        <v>53.99098122449773</v>
+        <f t="shared" si="22"/>
+        <v>109.60967301818046</v>
       </c>
       <c r="DU15" s="2">
-        <f t="shared" si="17"/>
-        <v>53.451071412252752</v>
+        <f t="shared" si="22"/>
+        <v>108.51357628799866</v>
       </c>
       <c r="DV15" s="2">
-        <f t="shared" si="17"/>
-        <v>52.916560698130226</v>
+        <f t="shared" si="22"/>
+        <v>107.42844052511867</v>
       </c>
       <c r="DW15" s="2">
-        <f t="shared" si="17"/>
-        <v>52.387395091148925</v>
+        <f t="shared" si="22"/>
+        <v>106.35415611986748</v>
       </c>
       <c r="DX15" s="2">
-        <f t="shared" si="17"/>
-        <v>51.863521140237438</v>
+        <f t="shared" si="22"/>
+        <v>105.29061455866881</v>
       </c>
       <c r="DY15" s="2">
-        <f t="shared" si="17"/>
-        <v>51.344885928835062</v>
+        <f t="shared" si="22"/>
+        <v>104.23770841308212</v>
       </c>
       <c r="DZ15" s="2">
-        <f t="shared" si="17"/>
-        <v>50.831437069546709</v>
+        <f t="shared" si="22"/>
+        <v>103.1953313289513</v>
       </c>
       <c r="EA15" s="2">
-        <f t="shared" si="17"/>
-        <v>50.323122698851243</v>
+        <f t="shared" si="22"/>
+        <v>102.16337801566178</v>
       </c>
       <c r="EB15" s="2">
-        <f t="shared" si="17"/>
-        <v>49.819891471862732</v>
+        <f t="shared" si="22"/>
+        <v>101.14174423550516</v>
       </c>
       <c r="EC15" s="2">
-        <f t="shared" si="17"/>
-        <v>49.321692557144104</v>
+        <f t="shared" si="22"/>
+        <v>100.1303267931501</v>
       </c>
       <c r="ED15" s="2">
-        <f t="shared" si="17"/>
-        <v>48.828475631572665</v>
+        <f t="shared" si="22"/>
+        <v>99.129023525218599</v>
       </c>
     </row>
     <row r="16" spans="2:134" x14ac:dyDescent="0.3">
@@ -2287,6 +2382,10 @@
         <f>99.8</f>
         <v>99.8</v>
       </c>
+      <c r="E16" s="4">
+        <f>119.4</f>
+        <v>119.4</v>
+      </c>
       <c r="F16" s="4">
         <f>99.8</f>
         <v>99.8</v>
@@ -2300,56 +2399,60 @@
         <v>99.8</v>
       </c>
       <c r="I16" s="4">
-        <f>99.8+18</f>
-        <v>117.8</v>
+        <f>119.4</f>
+        <v>119.4</v>
       </c>
       <c r="J16" s="4">
-        <f>99.8+18</f>
-        <v>117.8</v>
+        <f>119.4</f>
+        <v>119.4</v>
+      </c>
+      <c r="N16" s="4">
+        <f t="shared" ref="N16:Y16" si="23">119.4</f>
+        <v>119.4</v>
       </c>
       <c r="O16" s="4">
-        <f>99.8</f>
-        <v>99.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="P16" s="4">
-        <f>99.8+18</f>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="Q16" s="4">
-        <f t="shared" ref="Q16:Y16" si="18">99.8+18</f>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="R16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="S16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="T16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="U16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="V16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="W16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="X16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
       <c r="Y16" s="4">
-        <f t="shared" si="18"/>
-        <v>117.8</v>
+        <f t="shared" si="23"/>
+        <v>119.4</v>
       </c>
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.3">
@@ -2357,85 +2460,97 @@
         <v>25</v>
       </c>
       <c r="C17" s="8">
-        <f>C15/C16</f>
+        <f t="shared" ref="C17:J17" si="24">C15/C16</f>
         <v>-5.5110220440881763E-2</v>
       </c>
       <c r="D17" s="8">
-        <f>D15/D16</f>
+        <f t="shared" si="24"/>
         <v>-8.2164328657314628E-2</v>
       </c>
+      <c r="E17" s="8">
+        <f t="shared" si="24"/>
+        <v>-0.10469011725293131</v>
+      </c>
       <c r="F17" s="8">
-        <f>F15/F16</f>
+        <f t="shared" si="24"/>
         <v>-0.13727454909819639</v>
       </c>
       <c r="G17" s="8">
-        <f>G15/G16</f>
+        <f t="shared" si="24"/>
         <v>-0.23146292585170342</v>
       </c>
       <c r="H17" s="8">
-        <f>H15/H16</f>
+        <f t="shared" si="24"/>
         <v>-0.13226452905811623</v>
       </c>
       <c r="I17" s="8">
-        <f>I15/I16</f>
-        <v>-0.12669779286926994</v>
+        <f t="shared" si="24"/>
+        <v>-0.13484087102177555</v>
       </c>
       <c r="J17" s="8">
-        <f>J15/J16</f>
-        <v>-0.1536502546689304</v>
+        <f t="shared" si="24"/>
+        <v>-0.14855527638190952</v>
+      </c>
+      <c r="N17" s="8">
+        <f>N15/N16</f>
+        <v>-0.33417085427135668</v>
       </c>
       <c r="O17" s="8">
         <f>O15/O16</f>
-        <v>-0.69463927855711427</v>
+        <v>-0.58741624790619762</v>
       </c>
       <c r="P17" s="8">
         <f>P15/P16</f>
-        <v>-0.77403650254668932</v>
+        <v>-0.86257328308207704</v>
       </c>
       <c r="Q17" s="8">
-        <f t="shared" ref="Q17:Y17" si="19">Q15/Q16</f>
-        <v>-0.93740135823429549</v>
+        <f t="shared" ref="Q17:Y17" si="25">Q15/Q16</f>
+        <v>-1.0852194304857621</v>
       </c>
       <c r="R17" s="8">
-        <f t="shared" si="19"/>
-        <v>-1.0498758709677418</v>
+        <f t="shared" si="25"/>
+        <v>-1.167126917922948</v>
       </c>
       <c r="S17" s="8">
-        <f t="shared" si="19"/>
-        <v>-1.0004894155517825</v>
+        <f t="shared" si="25"/>
+        <v>-0.96072711959798962</v>
       </c>
       <c r="T17" s="8">
-        <f t="shared" si="19"/>
-        <v>-0.74263847041629893</v>
+        <f t="shared" si="25"/>
+        <v>-0.46977399867336689</v>
       </c>
       <c r="U17" s="8">
-        <f t="shared" si="19"/>
-        <v>-0.43226223863617003</v>
+        <f t="shared" si="25"/>
+        <v>8.3617873111959132E-2</v>
       </c>
       <c r="V17" s="8">
-        <f t="shared" si="19"/>
-        <v>1.8916503874637967E-2</v>
+        <f t="shared" si="25"/>
+        <v>0.78659088421741463</v>
       </c>
       <c r="W17" s="8">
-        <f t="shared" si="19"/>
-        <v>0.48508693387403246</v>
+        <f t="shared" si="25"/>
+        <v>1.445892831778647</v>
       </c>
       <c r="X17" s="8">
-        <f t="shared" si="19"/>
-        <v>0.93153077423874542</v>
+        <f t="shared" si="25"/>
+        <v>2.0999872195582658</v>
       </c>
       <c r="Y17" s="8">
-        <f t="shared" si="19"/>
-        <v>1.2396288205421306</v>
+        <f t="shared" si="25"/>
+        <v>2.4829060701268362</v>
       </c>
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="I19" s="10">
+        <f>I3/E3-1</f>
+        <v>6.3846153846153841</v>
+      </c>
       <c r="J19" s="10">
         <f>J3/F3-1</f>
-        <v>1.6666666666666665</v>
+        <v>5.5</v>
       </c>
       <c r="O19" s="10"/>
       <c r="P19" s="10">
@@ -2443,40 +2558,40 @@
         <v>1.5</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" ref="Q19:Y19" si="20">Q3/P3-1</f>
-        <v>1.2000000000000002</v>
+        <f t="shared" ref="Q19:Y19" si="26">Q3/P3-1</f>
+        <v>1</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="20"/>
-        <v>1</v>
+        <f t="shared" si="26"/>
+        <v>0.89999999999999991</v>
       </c>
       <c r="S19" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.8</v>
       </c>
       <c r="T19" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.7</v>
       </c>
       <c r="U19" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0.5</v>
       </c>
       <c r="V19" s="10">
-        <f t="shared" si="20"/>
-        <v>0.39999999999999991</v>
+        <f t="shared" si="26"/>
+        <v>0.35000000000000009</v>
       </c>
       <c r="W19" s="10">
-        <f t="shared" si="20"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="26"/>
+        <v>0.25</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" si="20"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="26"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" si="20"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="26"/>
+        <v>0.12000000000000011</v>
       </c>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.3">
@@ -2484,11 +2599,11 @@
         <v>34</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" ref="F20:G20" si="21">F5/F3</f>
+        <f t="shared" ref="F20:G20" si="27">F5/F3</f>
         <v>-6.6666666666666721E-2</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>-0.56249999999999989</v>
       </c>
       <c r="H20" s="10">
@@ -2496,55 +2611,55 @@
         <v>0.12500000000000011</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" ref="I20:J20" si="22">I5/I3</f>
-        <v>0.14999999999999997</v>
+        <f t="shared" ref="I20:J20" si="28">I5/I3</f>
+        <v>6.2499999999999965E-2</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="22"/>
-        <v>0.15000000000000002</v>
+        <f t="shared" si="28"/>
+        <v>0.15000000000000005</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" ref="O20:Y20" si="23">O5/O3</f>
-        <v>5.08130081300813E-2</v>
+        <f t="shared" ref="O20:Y20" si="29">O5/O3</f>
+        <v>6.4699792960662528E-2</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="23"/>
-        <v>0.19</v>
+        <f t="shared" si="29"/>
+        <v>0.15</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="23"/>
-        <v>0.24</v>
+        <f t="shared" si="29"/>
+        <v>0.2</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="23"/>
-        <v>0.27</v>
+        <f t="shared" si="29"/>
+        <v>0.25</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0.3</v>
       </c>
       <c r="AA20" s="1" t="s">
@@ -2557,6 +2672,10 @@
     <row r="21" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>35</v>
+      </c>
+      <c r="I21" s="10">
+        <f>I5/E5-1</f>
+        <v>-2.4999999999999991</v>
       </c>
       <c r="J21" s="10">
         <f>J6/F6-1</f>
@@ -2568,39 +2687,39 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" ref="Q21:Y21" si="24">Q6/P6-1</f>
-        <v>0.39999999999999991</v>
+        <f t="shared" ref="Q21:Y21" si="30">Q6/P6-1</f>
+        <v>0.39999999999999969</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA21" s="1" t="s">
@@ -2615,11 +2734,11 @@
         <v>36</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" ref="F22:G22" si="25">F7/F3</f>
+        <f t="shared" ref="F22:G22" si="31">F7/F3</f>
         <v>1.5333333333333332</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>2.0624999999999996</v>
       </c>
       <c r="H22" s="10">
@@ -2627,69 +2746,73 @@
         <v>1</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:J22" si="26">I7/I3</f>
-        <v>0.9</v>
+        <f t="shared" ref="I22:J22" si="32">I7/I3</f>
+        <v>0.3125</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="26"/>
-        <v>0.85</v>
+        <f t="shared" si="32"/>
+        <v>0.4</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" ref="O22:Y22" si="27">O7/O3</f>
-        <v>1.0609756097560976</v>
+        <f t="shared" ref="O22:Y22" si="33">O7/O3</f>
+        <v>0.55486542443064191</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="27"/>
-        <v>0.6</v>
+        <f t="shared" si="33"/>
+        <v>0.5</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.4</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.3</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.2</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.15</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.13</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.11</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="27"/>
-        <v>0.1</v>
+        <f t="shared" si="33"/>
+        <v>0.10000000000000002</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.09</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0.09</v>
       </c>
       <c r="AA22" s="1" t="s">
         <v>42</v>
       </c>
       <c r="AB22" s="4">
-        <f>NPV(AB21,P15:ED15)</f>
-        <v>125.50532601399057</v>
+        <f>NPV(AB21,O15:ED15)</f>
+        <v>640.04140600785081</v>
       </c>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="I23" s="10">
+        <f>I7/E7-1</f>
+        <v>0.5</v>
+      </c>
       <c r="J23" s="10">
         <f>J8/F8-1</f>
         <v>0.62222222222222223</v>
@@ -2697,42 +2820,42 @@
       <c r="O23" s="10"/>
       <c r="P23" s="10">
         <f>P8/O8-1</f>
-        <v>0.5</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="Q23" s="10">
-        <f t="shared" ref="Q23:Y23" si="28">Q8/P8-1</f>
+        <f t="shared" ref="Q23:Y23" si="34">Q8/P8-1</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA23" s="1" t="s">
@@ -2740,7 +2863,7 @@
       </c>
       <c r="AB23" s="4">
         <f>Main!D8</f>
-        <v>46.100000000000009</v>
+        <v>192.6</v>
       </c>
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.3">
@@ -2748,11 +2871,11 @@
         <v>38</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" ref="F24:G24" si="29">F11/F3</f>
+        <f t="shared" ref="F24:G24" si="35">F11/F3</f>
         <v>-6.333333333333333</v>
       </c>
       <c r="G24" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>-7.8125</v>
       </c>
       <c r="H24" s="10">
@@ -2760,63 +2883,63 @@
         <v>-3.9374999999999996</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" ref="I24:J24" si="30">I11/I3</f>
-        <v>-3.6928571428571426</v>
+        <f t="shared" ref="I24:J24" si="36">I11/I3</f>
+        <v>-1.8333333333333335</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="30"/>
-        <v>-3.5249999999999999</v>
+        <f t="shared" si="36"/>
+        <v>-1.4089743589743589</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" ref="O24:Y24" si="31">O11/O3</f>
-        <v>-4.23780487804878</v>
+        <f t="shared" ref="O24:Y24" si="37">O11/O3</f>
+        <v>-2.3369565217391304</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="31"/>
-        <v>-2.3947154471544718</v>
+        <f t="shared" si="37"/>
+        <v>-1.4862318840579711</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" si="31"/>
-        <v>-1.3677900960827789</v>
+        <f t="shared" si="37"/>
+        <v>-0.96107660455486532</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="31"/>
-        <v>-0.77917664449371749</v>
+        <f t="shared" si="37"/>
+        <v>-0.54727797755257712</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" si="31"/>
-        <v>-0.40748879034244878</v>
+        <f t="shared" si="37"/>
+        <v>-0.24369910282953752</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="31"/>
-        <v>-0.16543392316276107</v>
+        <f t="shared" si="37"/>
+        <v>-5.9452360654406698E-2</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="31"/>
-        <v>-5.0803746213932764E-2</v>
+        <f t="shared" si="37"/>
+        <v>2.3383347541915244E-2</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="31"/>
-        <v>2.5287326637972233E-2</v>
+        <f t="shared" si="37"/>
+        <v>7.6568242905264455E-2</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="31"/>
-        <v>6.8387058823529398E-2</v>
+        <f t="shared" si="37"/>
+        <v>0.10572140999386782</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="31"/>
-        <v>9.6061130320420823E-2</v>
+        <f t="shared" si="37"/>
+        <v>0.12698448222509351</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" si="31"/>
-        <v>0.10706375156675606</v>
+        <f t="shared" si="37"/>
+        <v>0.13297897114474982</v>
       </c>
       <c r="AA24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="AB24" s="4">
         <f>AB22+AB23</f>
-        <v>171.60532601399058</v>
+        <v>832.64140600785083</v>
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.3">
@@ -2828,7 +2951,7 @@
       </c>
       <c r="AB25" s="3">
         <f>AB24/Y16</f>
-        <v>1.4567514941764905</v>
+        <v>6.9735461139685997</v>
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.3">
@@ -2836,11 +2959,11 @@
         <v>39</v>
       </c>
       <c r="F26" s="10">
-        <f t="shared" ref="F26:G26" si="32">F15/F3</f>
+        <f t="shared" ref="F26:G26" si="38">F15/F3</f>
         <v>-9.1333333333333329</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>-14.4375</v>
       </c>
       <c r="H26" s="10">
@@ -2848,63 +2971,63 @@
         <v>-4.1249999999999991</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" ref="I26:J26" si="33">I15/I3</f>
-        <v>-4.2642857142857142</v>
+        <f t="shared" ref="I26:J26" si="39">I15/I3</f>
+        <v>-1.6770833333333335</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="33"/>
-        <v>-4.5250000000000004</v>
+        <f t="shared" si="39"/>
+        <v>-1.819230769230769</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" ref="O26:Y26" si="34">O15/O3</f>
-        <v>-5.6361788617886175</v>
+        <f t="shared" ref="O26:Y26" si="40">O15/O3</f>
+        <v>-2.90424430641822</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="34"/>
-        <v>-2.9652520325203251</v>
+        <f t="shared" si="40"/>
+        <v>-1.7058592132505177</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="34"/>
-        <v>-1.6323116038433112</v>
+        <f t="shared" si="40"/>
+        <v>-1.0730865424430642</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="34"/>
-        <v>-0.91408261345158892</v>
+        <f t="shared" si="40"/>
+        <v>-0.60740962841887325</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="34"/>
-        <v>-0.48393550608524255</v>
+        <f t="shared" si="40"/>
+        <v>-0.27777370498710541</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="34"/>
-        <v>-0.21130195260843732</v>
+        <f t="shared" si="40"/>
+        <v>-7.9897121948947408E-2</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="34"/>
-        <v>-8.1994006236992642E-2</v>
+        <f t="shared" si="40"/>
+        <v>9.4809098616275671E-3</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="34"/>
-        <v>2.5629943354571797E-3</v>
+        <f t="shared" si="40"/>
+        <v>6.6064178880158211E-2</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="34"/>
-        <v>5.0557198093863748E-2</v>
+        <f t="shared" si="40"/>
+        <v>9.7150093749381133E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="34"/>
-        <v>8.0905748700205005E-2</v>
+        <f t="shared" si="40"/>
+        <v>0.1195753783527406</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="34"/>
-        <v>9.3621586999260292E-2</v>
+        <f t="shared" si="40"/>
+        <v>0.126231394403857</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>46</v>
       </c>
       <c r="AB26" s="3">
         <f>Main!D3</f>
-        <v>11.52</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.3">
@@ -2913,7 +3036,7 @@
       </c>
       <c r="AB27" s="11">
         <f>AB25/AB26-1</f>
-        <v>-0.87354587724162402</v>
+        <v>9.6469514774937037E-2</v>
       </c>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.3">
@@ -2921,12 +3044,12 @@
         <v>48</v>
       </c>
       <c r="AB28" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="2:28" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F29" s="12">
         <f>55.6</f>
@@ -2935,23 +3058,33 @@
       <c r="H29" s="12">
         <v>121.4</v>
       </c>
+      <c r="I29" s="12">
+        <v>286</v>
+      </c>
+      <c r="O29" s="12">
+        <v>286</v>
+      </c>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" s="13">
-        <f>Main!D9/Model!H29</f>
-        <v>10.798649093904446</v>
+        <v>50</v>
+      </c>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="O31" s="13">
+        <f>Main!$D$9/Model!O29</f>
+        <v>1.9817622377622381</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="10">
-        <f>H29/Main!D9-1</f>
-        <v>-0.90739582411614117</v>
+        <v>51</v>
+      </c>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="O32" s="10">
+        <f>O29/Main!$D$9-1</f>
+        <v>-0.49539859981933165</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/RCAT.xlsx
+++ b/Financial Analysis/RCAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9A9DCE-D65A-4535-8802-16EEF59C7B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849E8F42-6E9B-4FE6-92DD-B27F693383F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{274E4BE5-5FA1-49CC-A03D-A4474EC70AFC}"/>
   </bookViews>
@@ -184,7 +184,7 @@
     <t>B/EV</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -751,14 +751,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>6.36</v>
+        <v>12.34</v>
       </c>
       <c r="E3" s="6">
-        <v>45983</v>
+        <v>46071</v>
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45983</v>
+        <v>46071</v>
       </c>
       <c r="G3" s="6">
         <v>46078</v>
@@ -782,7 +782,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>759.38400000000013</v>
+        <v>1473.396</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +824,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>566.78400000000011</v>
+        <v>1280.796</v>
       </c>
     </row>
   </sheetData>
@@ -2726,7 +2726,7 @@
         <v>41</v>
       </c>
       <c r="AB21" s="10">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.3">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AB22" s="4">
         <f>NPV(AB21,O15:ED15)</f>
-        <v>640.04140600785081</v>
+        <v>813.58537297051816</v>
       </c>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.3">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AB24" s="4">
         <f>AB22+AB23</f>
-        <v>832.64140600785083</v>
+        <v>1006.1853729705182</v>
       </c>
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.3">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AB25" s="3">
         <f>AB24/Y16</f>
-        <v>6.9735461139685997</v>
+        <v>8.4270131739574392</v>
       </c>
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.3">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB26" s="3">
         <f>Main!D3</f>
-        <v>6.36</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.3">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB27" s="11">
         <f>AB25/AB26-1</f>
-        <v>9.6469514774937037E-2</v>
+        <v>-0.31709779789647985</v>
       </c>
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.3">
@@ -3073,7 +3073,7 @@
       <c r="I31" s="13"/>
       <c r="O31" s="13">
         <f>Main!$D$9/Model!O29</f>
-        <v>1.9817622377622381</v>
+        <v>4.4783076923076921</v>
       </c>
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.3">
@@ -3084,7 +3084,7 @@
       <c r="I32" s="10"/>
       <c r="O32" s="10">
         <f>O29/Main!$D$9-1</f>
-        <v>-0.49539859981933165</v>
+        <v>-0.77670136383936239</v>
       </c>
     </row>
   </sheetData>
